--- a/2026_Financials.xlsx
+++ b/2026_Financials.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hanks\DnD-Homebrew\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DEA5856-A016-4331-BF72-4BF82D1E15B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3342E20-8089-4D38-9D99-024810F2E08A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" firstSheet="4" activeTab="8" xr2:uid="{A55BF991-A51A-40F9-BCC2-CFBADEB3BEC2}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" firstSheet="6" activeTab="9" xr2:uid="{A55BF991-A51A-40F9-BCC2-CFBADEB3BEC2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,6 +22,7 @@
     <sheet name="MarchContent(Desert)" sheetId="7" r:id="rId7"/>
     <sheet name="MayContent(FelDwarves)" sheetId="10" r:id="rId8"/>
     <sheet name="AugustContent(EmpireSoldiers)" sheetId="11" r:id="rId9"/>
+    <sheet name="OctoberContent(UndeadMinions)" sheetId="12" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="267">
   <si>
     <t>Heated Desk Pad</t>
   </si>
@@ -548,9 +549,6 @@
     <t>May</t>
   </si>
   <si>
-    <t>June</t>
-  </si>
-  <si>
     <t>Hobgoblins Part 1</t>
   </si>
   <si>
@@ -668,9 +666,6 @@
     <t>September</t>
   </si>
   <si>
-    <t>Generals</t>
-  </si>
-  <si>
     <t>Simple Melee Soldiers</t>
   </si>
   <si>
@@ -711,6 +706,135 @@
   </si>
   <si>
     <t>Added Extra Archer &amp; Crossbowman</t>
+  </si>
+  <si>
+    <t>Zombie RoR (The Tithe)</t>
+  </si>
+  <si>
+    <t>Skeleton</t>
+  </si>
+  <si>
+    <t>Skeleton RoR</t>
+  </si>
+  <si>
+    <t>Ghoul RoR</t>
+  </si>
+  <si>
+    <t>Grave Guard</t>
+  </si>
+  <si>
+    <t>Grave Guard (RoR)</t>
+  </si>
+  <si>
+    <t>Cairn Wraith</t>
+  </si>
+  <si>
+    <t>Hex Wraiths</t>
+  </si>
+  <si>
+    <t>Hex Wraiths (RoR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fel Bats </t>
+  </si>
+  <si>
+    <t>Dire Wolves</t>
+  </si>
+  <si>
+    <t>Dire Wolves (RoR)</t>
+  </si>
+  <si>
+    <t>Crypt Horrors</t>
+  </si>
+  <si>
+    <t>Corpse Cart</t>
+  </si>
+  <si>
+    <t>Mortis Engine</t>
+  </si>
+  <si>
+    <t>Black Coach</t>
+  </si>
+  <si>
+    <t>Spirit Host</t>
+  </si>
+  <si>
+    <t>Banshee</t>
+  </si>
+  <si>
+    <t>October</t>
+  </si>
+  <si>
+    <t>November</t>
+  </si>
+  <si>
+    <t>Mourngul</t>
+  </si>
+  <si>
+    <t>Mourngul (RoR)</t>
+  </si>
+  <si>
+    <t>Breath of Darkness</t>
+  </si>
+  <si>
+    <t>Soul Stealer</t>
+  </si>
+  <si>
+    <t>Abyssal Swarm</t>
+  </si>
+  <si>
+    <t>Dark Riders</t>
+  </si>
+  <si>
+    <t>Harbinger</t>
+  </si>
+  <si>
+    <t>Morghast Harbingers</t>
+  </si>
+  <si>
+    <t>Morghast Archai</t>
+  </si>
+  <si>
+    <t>Morghast Archai (RoR)</t>
+  </si>
+  <si>
+    <t>December</t>
+  </si>
+  <si>
+    <t>Skeletons</t>
+  </si>
+  <si>
+    <t>Zombies</t>
+  </si>
+  <si>
+    <t>Ghouls &amp; Crypt Horrors</t>
+  </si>
+  <si>
+    <t>Morngul</t>
+  </si>
+  <si>
+    <t>Morghasts</t>
+  </si>
+  <si>
+    <t>Wraiths</t>
+  </si>
+  <si>
+    <t>Fel Bats</t>
+  </si>
+  <si>
+    <t>Racial Traits For NPCs</t>
+  </si>
+  <si>
+    <t>July</t>
+  </si>
+  <si>
+    <t>Generals Start</t>
+  </si>
+  <si>
+    <t>Generals Finish</t>
+  </si>
+  <si>
+    <t>Scope Creep</t>
   </si>
 </sst>
 </file>
@@ -784,7 +908,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -815,10 +939,28 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1145,7 +1287,7 @@
       <c r="A1" s="1">
         <v>27.35</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="18" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1153,55 +1295,55 @@
       <c r="A2" s="1">
         <v>39.24</v>
       </c>
-      <c r="B2" s="14"/>
+      <c r="B2" s="18"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>15.3</v>
       </c>
-      <c r="B3" s="14"/>
+      <c r="B3" s="18"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>43.18</v>
       </c>
-      <c r="B4" s="14"/>
+      <c r="B4" s="18"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>49.9</v>
       </c>
-      <c r="B5" s="14"/>
+      <c r="B5" s="18"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>42.26</v>
       </c>
-      <c r="B6" s="14"/>
+      <c r="B6" s="18"/>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>72.63</v>
       </c>
-      <c r="B7" s="14"/>
+      <c r="B7" s="18"/>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>65.540000000000006</v>
       </c>
-      <c r="B8" s="14"/>
+      <c r="B8" s="18"/>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>49.93</v>
       </c>
-      <c r="B9" s="14"/>
+      <c r="B9" s="18"/>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>56.15</v>
       </c>
-      <c r="B10" s="14"/>
+      <c r="B10" s="18"/>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
@@ -1304,6 +1446,1101 @@
     <mergeCell ref="B1:B10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99ADC6FB-BFB5-4C35-92F4-87AD55CB0E6A}">
+  <dimension ref="A1:R52"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="42" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.08984375" customWidth="1"/>
+    <col min="12" max="12" width="26.90625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="28.6328125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.54296875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" t="s">
+        <v>242</v>
+      </c>
+      <c r="M1" t="s">
+        <v>145</v>
+      </c>
+      <c r="O1" t="s">
+        <v>243</v>
+      </c>
+      <c r="P1" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>254</v>
+      </c>
+      <c r="R1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A2" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="B2" s="1">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1">
+        <v>10</v>
+      </c>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2">
+        <f>(B2*C2)+D2+E2+F2</f>
+        <v>10</v>
+      </c>
+      <c r="H2" s="3"/>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2" s="20" t="s">
+        <v>256</v>
+      </c>
+      <c r="M2" s="17">
+        <v>20</v>
+      </c>
+      <c r="N2" s="17">
+        <v>1</v>
+      </c>
+      <c r="O2" s="15" t="s">
+        <v>259</v>
+      </c>
+      <c r="P2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A3" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="B3" s="1">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1">
+        <v>10</v>
+      </c>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3">
+        <f t="shared" ref="G3:G34" si="0">(B3*C3)+D3+E3+F3</f>
+        <v>10</v>
+      </c>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3" s="20" t="s">
+        <v>255</v>
+      </c>
+      <c r="M3" s="17">
+        <v>20</v>
+      </c>
+      <c r="N3" s="17">
+        <v>1</v>
+      </c>
+      <c r="O3" s="14" t="s">
+        <v>238</v>
+      </c>
+      <c r="P3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A4" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="B4" s="1">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1">
+        <v>10</v>
+      </c>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4" s="21" t="s">
+        <v>257</v>
+      </c>
+      <c r="M4">
+        <v>26</v>
+      </c>
+      <c r="N4">
+        <v>2</v>
+      </c>
+      <c r="O4" s="14" t="s">
+        <v>239</v>
+      </c>
+      <c r="P4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A5" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="B5" s="1">
+        <v>1</v>
+      </c>
+      <c r="C5" s="1">
+        <v>10</v>
+      </c>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5" s="21" t="s">
+        <v>228</v>
+      </c>
+      <c r="M5">
+        <v>26</v>
+      </c>
+      <c r="N5">
+        <v>1</v>
+      </c>
+      <c r="O5" s="21" t="s">
+        <v>234</v>
+      </c>
+      <c r="P5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B6" s="1">
+        <v>1</v>
+      </c>
+      <c r="C6" s="1">
+        <v>16</v>
+      </c>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="M6">
+        <v>30</v>
+      </c>
+      <c r="N6">
+        <v>3</v>
+      </c>
+      <c r="O6" s="21" t="s">
+        <v>143</v>
+      </c>
+      <c r="P6">
+        <v>52</v>
+      </c>
+      <c r="Q6" s="1"/>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B7" s="1">
+        <v>1</v>
+      </c>
+      <c r="C7" s="1">
+        <v>10</v>
+      </c>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7" s="21" t="s">
+        <v>240</v>
+      </c>
+      <c r="M7">
+        <v>16</v>
+      </c>
+      <c r="N7">
+        <v>1</v>
+      </c>
+      <c r="O7" s="16" t="s">
+        <v>258</v>
+      </c>
+      <c r="P7">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8">
+        <f>(B8*C8)+D8+E8+F8</f>
+        <v>0</v>
+      </c>
+      <c r="H8" s="3"/>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>237</v>
+      </c>
+      <c r="M8">
+        <v>30</v>
+      </c>
+      <c r="N8">
+        <v>2</v>
+      </c>
+      <c r="O8" s="20" t="s">
+        <v>172</v>
+      </c>
+      <c r="P8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9">
+        <f>(B9*C9)+D9+E9+F9</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="1"/>
+      <c r="K9">
+        <v>2</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>260</v>
+      </c>
+      <c r="M9">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="L10" s="21" t="s">
+        <v>241</v>
+      </c>
+      <c r="M10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11">
+        <f>(B11*C11)+D11+E11+F11</f>
+        <v>0</v>
+      </c>
+      <c r="H11" s="1"/>
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="L11" s="20" t="s">
+        <v>261</v>
+      </c>
+      <c r="M11">
+        <v>16</v>
+      </c>
+      <c r="O11" s="1"/>
+      <c r="Q11" s="1"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="K12" t="s">
+        <v>266</v>
+      </c>
+      <c r="L12" s="1"/>
+      <c r="M12">
+        <v>30</v>
+      </c>
+      <c r="O12" s="1"/>
+      <c r="P12">
+        <v>20</v>
+      </c>
+      <c r="Q12" s="1"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A13" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="B13" s="1">
+        <v>1</v>
+      </c>
+      <c r="C13" s="1">
+        <v>16</v>
+      </c>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="H13" s="1"/>
+      <c r="L13" t="s">
+        <v>173</v>
+      </c>
+      <c r="M13">
+        <f>SUM(M2:M12)</f>
+        <v>266</v>
+      </c>
+      <c r="O13" t="s">
+        <v>173</v>
+      </c>
+      <c r="P13">
+        <f>SUM(P2:P12)</f>
+        <v>254</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>173</v>
+      </c>
+      <c r="R13">
+        <f>SUM(R2:R11)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A14" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="B14" s="1">
+        <v>1</v>
+      </c>
+      <c r="C14" s="1">
+        <v>10</v>
+      </c>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="H14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A15" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="B15" s="1">
+        <v>1</v>
+      </c>
+      <c r="C15" s="1">
+        <v>10</v>
+      </c>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="H15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A16" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="B16" s="1">
+        <v>1</v>
+      </c>
+      <c r="C16" s="1">
+        <v>16</v>
+      </c>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="H16" s="3"/>
+      <c r="P16" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17">
+        <f>(B17*C17)+D17+E17+F17</f>
+        <v>0</v>
+      </c>
+      <c r="H17" s="3"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H18" s="3"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A19" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B19" s="1">
+        <v>1</v>
+      </c>
+      <c r="C19" s="1">
+        <v>30</v>
+      </c>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="H19" s="3"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H20" s="3"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B21" s="1">
+        <v>1</v>
+      </c>
+      <c r="C21" s="1">
+        <v>30</v>
+      </c>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="H21" s="3"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A22" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="B22" s="1">
+        <v>1</v>
+      </c>
+      <c r="C22" s="1">
+        <v>10</v>
+      </c>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="H22" s="1"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H23" s="1"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H24" s="1"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A25" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="B25" s="1">
+        <v>1</v>
+      </c>
+      <c r="C25" s="1">
+        <v>4</v>
+      </c>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="H25" s="1"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A26" s="10" t="s">
+        <v>247</v>
+      </c>
+      <c r="B26" s="1">
+        <v>1</v>
+      </c>
+      <c r="C26" s="1">
+        <v>4</v>
+      </c>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="H26" s="1"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A27" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="B27" s="1">
+        <v>1</v>
+      </c>
+      <c r="C27" s="1">
+        <v>4</v>
+      </c>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="H27" s="1"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A28" s="14" t="s">
+        <v>249</v>
+      </c>
+      <c r="B28" s="1">
+        <v>1</v>
+      </c>
+      <c r="C28" s="1">
+        <v>4</v>
+      </c>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="H28" s="1"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A29" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="B29" s="1">
+        <v>1</v>
+      </c>
+      <c r="C29" s="1">
+        <v>4</v>
+      </c>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="H29" s="1"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A30" s="11"/>
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H30" s="1"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A31" s="11"/>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H31" s="1"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A32" s="11"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H32" s="1"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A33" s="11"/>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+      <c r="G33">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H33" s="1"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A34" s="11"/>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="G34">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H34" s="1"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A35" s="11"/>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="H35" s="1"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A36" s="1"/>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="H36" s="1"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A37" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B37" s="2"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1">
+        <f>SUM(G2:G34)</f>
+        <v>208</v>
+      </c>
+      <c r="H37" s="1">
+        <f>SUM(H2:H9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A38" s="2"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A39" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B39" s="2"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A40" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B40" s="1">
+        <v>1</v>
+      </c>
+      <c r="C40" s="1">
+        <v>30</v>
+      </c>
+      <c r="D40" s="1"/>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1"/>
+      <c r="G40" s="1">
+        <f>SUM(C40:F40)</f>
+        <v>30</v>
+      </c>
+      <c r="H40" s="3"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A41" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B41" s="1">
+        <v>1</v>
+      </c>
+      <c r="C41" s="1">
+        <v>30</v>
+      </c>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
+      <c r="G41" s="1">
+        <f t="shared" ref="G41:G45" si="1">SUM(C41:F41)</f>
+        <v>30</v>
+      </c>
+      <c r="H41" s="3"/>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A42" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="B42" s="1">
+        <v>1</v>
+      </c>
+      <c r="C42" s="1">
+        <v>16</v>
+      </c>
+      <c r="D42" s="1"/>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1"/>
+      <c r="G42" s="1">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="H42" s="3"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A43" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="B43" s="1">
+        <v>1</v>
+      </c>
+      <c r="C43" s="1">
+        <v>16</v>
+      </c>
+      <c r="D43" s="1"/>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="H43" s="3"/>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A44" s="11" t="s">
+        <v>252</v>
+      </c>
+      <c r="B44" s="1">
+        <v>1</v>
+      </c>
+      <c r="C44" s="1">
+        <v>10</v>
+      </c>
+      <c r="D44" s="1"/>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="1">
+        <f t="shared" ref="G44" si="2">SUM(C44:F44)</f>
+        <v>10</v>
+      </c>
+      <c r="H44" s="3"/>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A45" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="B45" s="1">
+        <v>1</v>
+      </c>
+      <c r="C45" s="1">
+        <v>10</v>
+      </c>
+      <c r="D45" s="1"/>
+      <c r="E45" s="1"/>
+      <c r="F45" s="1"/>
+      <c r="G45" s="1">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="H45" s="3"/>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A46" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B46" s="1">
+        <v>1</v>
+      </c>
+      <c r="C46" s="1">
+        <v>16</v>
+      </c>
+      <c r="D46" s="1"/>
+      <c r="E46" s="1"/>
+      <c r="F46" s="1"/>
+      <c r="G46" s="1">
+        <f>SUM(C46:F46)</f>
+        <v>16</v>
+      </c>
+      <c r="H46" s="3"/>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A47" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B47" s="1">
+        <v>1</v>
+      </c>
+      <c r="C47" s="1">
+        <v>16</v>
+      </c>
+      <c r="D47" s="1"/>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1"/>
+      <c r="G47" s="1">
+        <f>SUM(C47:F47)</f>
+        <v>16</v>
+      </c>
+      <c r="H47" s="3"/>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A48" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B48" s="1">
+        <v>1</v>
+      </c>
+      <c r="C48" s="1">
+        <v>10</v>
+      </c>
+      <c r="D48" s="1"/>
+      <c r="E48" s="1"/>
+      <c r="F48" s="1"/>
+      <c r="G48" s="1">
+        <f>SUM(C48:F48)</f>
+        <v>10</v>
+      </c>
+      <c r="H48" s="1"/>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A49" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B49" s="1">
+        <v>1</v>
+      </c>
+      <c r="C49" s="1">
+        <v>30</v>
+      </c>
+      <c r="D49" s="1"/>
+      <c r="E49" s="1"/>
+      <c r="F49" s="1"/>
+      <c r="G49" s="1">
+        <f>SUM(C49:F49)</f>
+        <v>30</v>
+      </c>
+      <c r="H49" s="1"/>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A50" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B50" s="1">
+        <v>1</v>
+      </c>
+      <c r="C50" s="1">
+        <v>16</v>
+      </c>
+      <c r="D50" s="1"/>
+      <c r="E50" s="1"/>
+      <c r="F50" s="1"/>
+      <c r="G50" s="1">
+        <f>SUM(C50:F50)</f>
+        <v>16</v>
+      </c>
+      <c r="H50" s="1"/>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A51" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B51" s="2"/>
+      <c r="C51" s="1"/>
+      <c r="D51" s="1"/>
+      <c r="E51" s="1"/>
+      <c r="F51" s="1"/>
+      <c r="G51" s="1">
+        <f>SUM(G40:G50)</f>
+        <v>200</v>
+      </c>
+      <c r="H51" s="1">
+        <f>SUM(H40:H50)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A52" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B52" s="2"/>
+      <c r="C52" s="1"/>
+      <c r="D52" s="1"/>
+      <c r="E52" s="1"/>
+      <c r="F52" s="1"/>
+      <c r="G52" s="1">
+        <f>G37+G51</f>
+        <v>408</v>
+      </c>
+      <c r="H52" s="1">
+        <f>H37+H51</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2078,7 +3315,7 @@
         <f>SUM(C5:F5)</f>
         <v>28</v>
       </c>
-      <c r="H5" s="14">
+      <c r="H5" s="18">
         <v>4</v>
       </c>
     </row>
@@ -2097,7 +3334,7 @@
         <f>SUM(C6:F6)</f>
         <v>6</v>
       </c>
-      <c r="H6" s="14"/>
+      <c r="H6" s="18"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="G8" s="1">
@@ -2155,7 +3392,7 @@
         <f>SUM(C16:F16)</f>
         <v>8</v>
       </c>
-      <c r="H16" s="14">
+      <c r="H16" s="18">
         <v>1</v>
       </c>
     </row>
@@ -2170,7 +3407,7 @@
         <f>SUM(C17:F17)</f>
         <v>8</v>
       </c>
-      <c r="H17" s="14"/>
+      <c r="H17" s="18"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
@@ -2338,7 +3575,7 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="H4" s="14">
+      <c r="H4" s="18">
         <v>3</v>
       </c>
     </row>
@@ -2353,7 +3590,7 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="H5" s="14"/>
+      <c r="H5" s="18"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
@@ -2366,7 +3603,7 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="H6" s="14"/>
+      <c r="H6" s="18"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
@@ -2379,7 +3616,7 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="H7" s="14"/>
+      <c r="H7" s="18"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
@@ -2392,7 +3629,7 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="H8" s="14"/>
+      <c r="H8" s="18"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="G9" s="1">
@@ -2453,7 +3690,7 @@
         <f t="shared" ref="G16:G21" si="1">SUM(C16:F16)</f>
         <v>5</v>
       </c>
-      <c r="H16" s="14">
+      <c r="H16" s="18">
         <v>1</v>
       </c>
     </row>
@@ -2468,7 +3705,7 @@
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="H17" s="14"/>
+      <c r="H17" s="18"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
@@ -2481,7 +3718,7 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="H18" s="14"/>
+      <c r="H18" s="18"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
@@ -2494,7 +3731,7 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="H19" s="14">
+      <c r="H19" s="18">
         <v>1</v>
       </c>
     </row>
@@ -2509,7 +3746,7 @@
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="H20" s="14"/>
+      <c r="H20" s="18"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
@@ -2604,7 +3841,7 @@
       <c r="D2" s="6">
         <v>46056</v>
       </c>
-      <c r="E2" s="15">
+      <c r="E2" s="19">
         <v>2</v>
       </c>
     </row>
@@ -2621,7 +3858,7 @@
       <c r="D3" s="6">
         <v>46057</v>
       </c>
-      <c r="E3" s="15"/>
+      <c r="E3" s="19"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
@@ -2636,7 +3873,7 @@
       <c r="D4" s="6">
         <v>46058</v>
       </c>
-      <c r="E4" s="15"/>
+      <c r="E4" s="19"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
@@ -2651,7 +3888,7 @@
       <c r="D5" s="6">
         <v>46061</v>
       </c>
-      <c r="E5" s="15"/>
+      <c r="E5" s="19"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
@@ -2666,7 +3903,7 @@
       <c r="D6" s="6">
         <v>46061</v>
       </c>
-      <c r="E6" s="15"/>
+      <c r="E6" s="19"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
@@ -2675,7 +3912,7 @@
       <c r="B7" t="s">
         <v>65</v>
       </c>
-      <c r="E7" s="15"/>
+      <c r="E7" s="19"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
@@ -2690,7 +3927,7 @@
       <c r="D8" s="6">
         <v>46063</v>
       </c>
-      <c r="E8" s="15"/>
+      <c r="E8" s="19"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
@@ -2705,7 +3942,7 @@
       <c r="D9" s="6">
         <v>46061</v>
       </c>
-      <c r="E9" s="15">
+      <c r="E9" s="19">
         <v>1</v>
       </c>
     </row>
@@ -2722,7 +3959,7 @@
       <c r="D10" s="6">
         <v>46061</v>
       </c>
-      <c r="E10" s="15"/>
+      <c r="E10" s="19"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
@@ -2737,7 +3974,7 @@
       <c r="D11" s="6">
         <v>46063</v>
       </c>
-      <c r="E11" s="15"/>
+      <c r="E11" s="19"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
@@ -2746,7 +3983,7 @@
       <c r="B12" t="s">
         <v>64</v>
       </c>
-      <c r="E12" s="15"/>
+      <c r="E12" s="19"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
@@ -2777,7 +4014,7 @@
       <c r="D15" s="6">
         <v>46076</v>
       </c>
-      <c r="E15" s="15">
+      <c r="E15" s="19">
         <v>3</v>
       </c>
     </row>
@@ -2794,7 +4031,7 @@
       <c r="D16" s="6">
         <v>46072</v>
       </c>
-      <c r="E16" s="15"/>
+      <c r="E16" s="19"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
@@ -2809,7 +4046,7 @@
       <c r="D17" s="6">
         <v>46073</v>
       </c>
-      <c r="E17" s="15"/>
+      <c r="E17" s="19"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
@@ -2824,7 +4061,7 @@
       <c r="D18" s="6">
         <v>46076</v>
       </c>
-      <c r="E18" s="15"/>
+      <c r="E18" s="19"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
@@ -2839,7 +4076,7 @@
       <c r="D19" s="6">
         <v>46078</v>
       </c>
-      <c r="E19" s="15"/>
+      <c r="E19" s="19"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
@@ -2851,7 +4088,7 @@
       <c r="C20">
         <v>30</v>
       </c>
-      <c r="E20" s="15"/>
+      <c r="E20" s="19"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
@@ -2863,7 +4100,7 @@
       <c r="C21">
         <v>30</v>
       </c>
-      <c r="E21" s="15"/>
+      <c r="E21" s="19"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
@@ -2878,7 +4115,7 @@
       <c r="D22" s="6">
         <v>46075</v>
       </c>
-      <c r="E22" s="15">
+      <c r="E22" s="19">
         <v>2</v>
       </c>
     </row>
@@ -2895,7 +4132,7 @@
       <c r="D23" s="6">
         <v>46076</v>
       </c>
-      <c r="E23" s="15"/>
+      <c r="E23" s="19"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
@@ -2910,7 +4147,7 @@
       <c r="D24" s="6">
         <v>46076</v>
       </c>
-      <c r="E24" s="15"/>
+      <c r="E24" s="19"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
@@ -2925,7 +4162,7 @@
       <c r="D25" s="6">
         <v>46076</v>
       </c>
-      <c r="E25" s="15"/>
+      <c r="E25" s="19"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
@@ -3108,7 +4345,7 @@
         <v>5</v>
       </c>
       <c r="H4" s="3"/>
-      <c r="K4" s="15">
+      <c r="K4" s="19">
         <v>7</v>
       </c>
       <c r="L4" s="7" t="s">
@@ -3146,7 +4383,7 @@
         <v>5</v>
       </c>
       <c r="H5" s="3"/>
-      <c r="K5" s="15"/>
+      <c r="K5" s="19"/>
       <c r="L5" s="8" t="s">
         <v>91</v>
       </c>
@@ -3182,7 +4419,7 @@
         <v>8</v>
       </c>
       <c r="H6" s="3"/>
-      <c r="O6" s="15">
+      <c r="O6" s="19">
         <v>4</v>
       </c>
       <c r="P6" s="7" t="s">
@@ -3223,7 +4460,7 @@
       <c r="N7" s="9">
         <v>4</v>
       </c>
-      <c r="O7" s="15"/>
+      <c r="O7" s="19"/>
       <c r="P7" s="8" t="s">
         <v>139</v>
       </c>
@@ -3291,7 +4528,7 @@
         <v>8</v>
       </c>
       <c r="H9" s="1"/>
-      <c r="O9" s="15">
+      <c r="O9" s="19">
         <v>3</v>
       </c>
       <c r="P9" s="8" t="s">
@@ -3320,7 +4557,7 @@
         <v>5</v>
       </c>
       <c r="H10" s="1"/>
-      <c r="O10" s="15"/>
+      <c r="O10" s="19"/>
       <c r="P10" s="10" t="s">
         <v>107</v>
       </c>
@@ -4454,7 +5691,7 @@
         <v>145</v>
       </c>
       <c r="N1" t="s">
-        <v>171</v>
+        <v>263</v>
       </c>
       <c r="O1" t="s">
         <v>145</v>
@@ -4482,7 +5719,7 @@
         <v>342</v>
       </c>
       <c r="L2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="M2">
         <v>36</v>
@@ -4514,7 +5751,7 @@
         <f t="shared" ref="G3:G20" si="0">(B3*C3)+D3+E3+F3</f>
         <v>10</v>
       </c>
-      <c r="H3" s="14">
+      <c r="H3" s="18">
         <v>66</v>
       </c>
       <c r="I3" s="3"/>
@@ -4522,13 +5759,13 @@
         <v>3</v>
       </c>
       <c r="L3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="M3">
         <v>30</v>
       </c>
       <c r="N3" s="8" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O3" s="8">
         <v>26</v>
@@ -4554,19 +5791,19 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="H4" s="14"/>
+      <c r="H4" s="18"/>
       <c r="I4" s="3"/>
       <c r="K4">
         <v>2</v>
       </c>
       <c r="L4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="M4">
         <v>50</v>
       </c>
       <c r="N4" s="8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="O4" s="8">
         <v>64</v>
@@ -4592,19 +5829,19 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="H5" s="14"/>
+      <c r="H5" s="18"/>
       <c r="I5" s="3"/>
       <c r="K5">
         <v>2</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="M5" s="8">
         <v>30</v>
       </c>
       <c r="N5" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="O5" s="8">
         <v>30</v>
@@ -4630,13 +5867,13 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="H6" s="14"/>
+      <c r="H6" s="18"/>
       <c r="I6" s="3"/>
       <c r="K6">
         <v>2</v>
       </c>
       <c r="L6" s="8" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="M6" s="8">
         <v>52</v>
@@ -4668,19 +5905,19 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="H7" s="14"/>
+      <c r="H7" s="18"/>
       <c r="I7" s="3"/>
       <c r="K7">
         <v>5</v>
       </c>
       <c r="L7" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="M7">
         <v>50</v>
       </c>
       <c r="N7" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="O7">
         <v>30</v>
@@ -4744,6 +5981,12 @@
         <v>50</v>
       </c>
       <c r="H9" s="1"/>
+      <c r="N9" t="s">
+        <v>262</v>
+      </c>
+      <c r="O9">
+        <v>16</v>
+      </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
@@ -4790,18 +6033,18 @@
       </c>
       <c r="H11" s="1"/>
       <c r="L11" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="M11">
         <f>SUM(M2:M10)</f>
         <v>294</v>
       </c>
       <c r="N11" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="O11">
         <f>SUM(O2:O10)</f>
-        <v>248</v>
+        <v>264</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.35">
@@ -4821,8 +6064,16 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="H12" s="14">
+      <c r="H12" s="18">
         <v>26</v>
+      </c>
+      <c r="M12">
+        <f>M11+M8*0.5</f>
+        <v>317</v>
+      </c>
+      <c r="O12">
+        <f>O11+O6*0.5</f>
+        <v>287</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.35">
@@ -4842,7 +6093,7 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="H13" s="14"/>
+      <c r="H13" s="18"/>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
@@ -4861,11 +6112,11 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="H14" s="14">
+      <c r="H14" s="18">
         <v>32</v>
       </c>
       <c r="O14" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.35">
@@ -4885,7 +6136,7 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="H15" s="14"/>
+      <c r="H15" s="18"/>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
@@ -4904,7 +6155,7 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="H16" s="14">
+      <c r="H16" s="18">
         <v>64</v>
       </c>
     </row>
@@ -4925,7 +6176,7 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="H17" s="14"/>
+      <c r="H17" s="18"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
@@ -4944,7 +6195,7 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="H18" s="14"/>
+      <c r="H18" s="18"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
@@ -4963,7 +6214,7 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="H19" s="14"/>
+      <c r="H19" s="18"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
@@ -5245,13 +6496,13 @@
       <c r="H1" s="2"/>
       <c r="K1" s="2"/>
       <c r="L1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="M1" t="s">
         <v>145</v>
       </c>
       <c r="N1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="O1" t="s">
         <v>145</v>
@@ -5259,7 +6510,7 @@
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B2" s="1">
         <v>1</v>
@@ -5279,10 +6530,10 @@
         <v>2</v>
       </c>
       <c r="L2" t="s">
-        <v>211</v>
+        <v>264</v>
       </c>
       <c r="M2">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="N2" s="1" t="s">
         <v>156</v>
@@ -5296,7 +6547,7 @@
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
@@ -5314,23 +6565,23 @@
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="K3">
         <v>3</v>
       </c>
       <c r="L3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="M3">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="N3" s="8"/>
       <c r="O3" s="8"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B4" s="1">
         <v>1</v>
@@ -5351,16 +6602,16 @@
         <v>1</v>
       </c>
       <c r="L4" s="12" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="M4" s="8">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="N4" s="13" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O4" s="13">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="P4">
         <v>1</v>
@@ -5368,7 +6619,7 @@
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -5385,16 +6636,16 @@
         <v>2</v>
       </c>
       <c r="L5" s="12" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="M5" s="13">
         <v>42</v>
       </c>
       <c r="N5" s="8" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="O5" s="8">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="P5">
         <v>2</v>
@@ -5402,7 +6653,7 @@
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B6" s="1">
         <v>1</v>
@@ -5423,13 +6674,13 @@
         <v>1</v>
       </c>
       <c r="L6" s="8" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="M6" s="8">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O6">
         <v>30</v>
@@ -5440,7 +6691,7 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B7" s="1">
         <v>1</v>
@@ -5458,22 +6709,22 @@
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
       <c r="J7" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="K7">
         <v>2</v>
       </c>
       <c r="L7" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="M7">
         <v>60</v>
       </c>
       <c r="N7" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="O7">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="P7">
         <v>2</v>
@@ -5481,7 +6732,7 @@
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B8" s="1">
         <v>1</v>
@@ -5498,10 +6749,10 @@
       </c>
       <c r="H8" s="3"/>
       <c r="N8" s="8" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="O8" s="8">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="P8">
         <v>1</v>
@@ -5509,7 +6760,7 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B9" s="1">
         <v>1</v>
@@ -5526,10 +6777,10 @@
       </c>
       <c r="H9" s="1"/>
       <c r="N9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O9">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="P9">
         <v>1</v>
@@ -5537,7 +6788,7 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B10" s="1">
         <v>1</v>
@@ -5553,11 +6804,16 @@
         <v>10</v>
       </c>
       <c r="H10" s="1"/>
-      <c r="N10" s="1"/>
+      <c r="N10" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="O10">
+        <v>10</v>
+      </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B11" s="1">
         <v>1</v>
@@ -5574,23 +6830,23 @@
       </c>
       <c r="H11" s="1"/>
       <c r="L11" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="M11">
         <f>SUM(M2:M10)</f>
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="N11" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="O11">
         <f>SUM(O2:O10)</f>
-        <v>222</v>
+        <v>272</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B12" s="1">
         <v>1</v>
@@ -5609,7 +6865,7 @@
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B13" s="1">
         <v>1</v>
@@ -5628,7 +6884,7 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B14" s="1">
         <v>1</v>
@@ -5645,12 +6901,12 @@
       </c>
       <c r="H14" s="3"/>
       <c r="O14" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B15" s="1">
         <v>1</v>
@@ -5669,7 +6925,7 @@
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B16" s="1">
         <v>1</v>
@@ -5688,7 +6944,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B17" s="1">
         <v>1</v>
@@ -5707,7 +6963,7 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B18" s="1">
         <v>1</v>
@@ -5726,7 +6982,7 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B19" s="1">
         <v>1</v>
@@ -5745,7 +7001,7 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B20" s="1">
         <v>1</v>
@@ -5764,7 +7020,7 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B21" s="1">
         <v>1</v>
@@ -5783,7 +7039,7 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -5798,7 +7054,7 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B23" s="1">
         <v>1</v>
@@ -5817,7 +7073,7 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B24" s="1">
         <v>1</v>
@@ -5836,7 +7092,7 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B25" s="1">
         <v>1</v>
@@ -5855,7 +7111,7 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" s="11" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B26" s="1">
         <v>1</v>
@@ -5897,7 +7153,7 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" s="11" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B28" s="1">
         <v>1</v>
@@ -5916,7 +7172,7 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" s="11" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B29" s="1">
         <v>1</v>
@@ -5935,7 +7191,7 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" s="11" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B30" s="1">
         <v>1</v>
@@ -5954,7 +7210,7 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" s="11" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -5969,7 +7225,7 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" s="11" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B32" s="1">
         <v>1</v>
@@ -5988,7 +7244,7 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" s="11" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B33" s="1">
         <v>1</v>

--- a/2026_Financials.xlsx
+++ b/2026_Financials.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hanks\DnD-Homebrew\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3342E20-8089-4D38-9D99-024810F2E08A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0366B8D5-34C7-4BF6-8C74-F87B6D60011C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" firstSheet="6" activeTab="9" xr2:uid="{A55BF991-A51A-40F9-BCC2-CFBADEB3BEC2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="6" activeTab="9" xr2:uid="{A55BF991-A51A-40F9-BCC2-CFBADEB3BEC2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -908,7 +908,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -955,12 +955,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1530,11 +1524,11 @@
       <c r="K2">
         <v>1</v>
       </c>
-      <c r="L2" s="20" t="s">
+      <c r="L2" s="1" t="s">
         <v>256</v>
       </c>
       <c r="M2" s="17">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="N2" s="17">
         <v>1</v>
@@ -1568,7 +1562,7 @@
       <c r="K3">
         <v>1</v>
       </c>
-      <c r="L3" s="20" t="s">
+      <c r="L3" s="1" t="s">
         <v>255</v>
       </c>
       <c r="M3" s="17">
@@ -1606,7 +1600,7 @@
       <c r="K4">
         <v>1</v>
       </c>
-      <c r="L4" s="21" t="s">
+      <c r="L4" s="11" t="s">
         <v>257</v>
       </c>
       <c r="M4">
@@ -1644,7 +1638,7 @@
       <c r="K5">
         <v>1</v>
       </c>
-      <c r="L5" s="21" t="s">
+      <c r="L5" s="11" t="s">
         <v>228</v>
       </c>
       <c r="M5">
@@ -1653,7 +1647,7 @@
       <c r="N5">
         <v>1</v>
       </c>
-      <c r="O5" s="21" t="s">
+      <c r="O5" s="11" t="s">
         <v>234</v>
       </c>
       <c r="P5">
@@ -1691,7 +1685,7 @@
       <c r="N6">
         <v>3</v>
       </c>
-      <c r="O6" s="21" t="s">
+      <c r="O6" s="11" t="s">
         <v>143</v>
       </c>
       <c r="P6">
@@ -1721,7 +1715,7 @@
       <c r="K7">
         <v>1</v>
       </c>
-      <c r="L7" s="21" t="s">
+      <c r="L7" s="11" t="s">
         <v>240</v>
       </c>
       <c r="M7">
@@ -1761,7 +1755,7 @@
       <c r="N8">
         <v>2</v>
       </c>
-      <c r="O8" s="20" t="s">
+      <c r="O8" s="1" t="s">
         <v>172</v>
       </c>
       <c r="P8">
@@ -1801,7 +1795,7 @@
       <c r="K10">
         <v>1</v>
       </c>
-      <c r="L10" s="21" t="s">
+      <c r="L10" s="11" t="s">
         <v>241</v>
       </c>
       <c r="M10">
@@ -1823,7 +1817,7 @@
       <c r="K11">
         <v>1</v>
       </c>
-      <c r="L11" s="20" t="s">
+      <c r="L11" s="1" t="s">
         <v>261</v>
       </c>
       <c r="M11">
@@ -1845,7 +1839,7 @@
       </c>
       <c r="L12" s="1"/>
       <c r="M12">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="O12" s="1"/>
       <c r="P12">
